--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,19 +581,19 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.133.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.133.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0133.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0133.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | candidate OCR token mismatch vs other OCR: "NorE" vs "NOTE" :: NorE.â€” This form may be varied according to the circumstances</t>
+          <t>L55: candidate OCR token mismatch vs other OCR: "NorE" vs "NOTE" :: NorE.— This form may be varied according to the circumstances</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr"/>
@@ -604,21 +604,21 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpÃ¦na, 4c.</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief : pray subpanaÃ¦na, &amp;c.</t>
-        </is>
-      </c>
+          <t>L139: suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpæna, 4c.</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”If 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]126 ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]126 ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L30: isolated marker/symbol line :: 126</t>
@@ -665,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -674,16 +674,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | candidate OCR token mismatch vs other OCR: "NorE" vs "NOTE" :: NorE.â€” This form may be varied according to the circumstances</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”This form may be varied according to the circumstances</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -708,7 +700,7 @@
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: â€”,deceased, and that C.D.,.,.,</t>
+          <t>L101: abbreviation/spacing may be garbled :: —,deceased, and that C.D.,.,.,</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr"/>
@@ -737,16 +729,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: estate and payment of his share thÃ©thereof.</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------â€”, who died on</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -754,7 +738,11 @@
           <t>L34: isolated marker/symbol line :: @</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L149: isolated marker/symbol line :: — ,</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
@@ -782,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -796,16 +784,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: â€”,deceased, and that C.D.,.,.,</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: estate of the said ------1â€”, deceased, and that C. D.,</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -851,16 +831,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: And for further relief; pray subpÃ¦na, &amp;., gc.</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”â€”, but ne</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -868,7 +840,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------â€”, who died on</t>
+          <t>L77: punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------—, who died on</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -903,11 +875,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about theâ€”</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -950,11 +918,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the (or the said A. B.â€™s share of the) personal estate of</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
@@ -962,7 +926,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: estate of the said ------1â€”, deceased, and that C. D.,</t>
+          <t>L82: punctuation artifact: double/multiple hyphen :: estate of the said ------1—, deceased, and that C. D.,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -997,11 +961,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpÃ¦na, 4c.</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
@@ -1029,12 +989,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1044,11 +1004,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” ,</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1077,7 +1033,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1116,7 +1072,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
